--- a/Day-04-Excel-Basics/Basics_filter_mathLogic.xlsx
+++ b/Day-04-Excel-Basics/Basics_filter_mathLogic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\90_Day_Data_Analytics\Day-04-Excel-Basics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22AB7B80-3D90-45E9-830E-76B9AF09F5B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91B13C7-CDB0-4171-9C03-AF8A604E2BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" xr2:uid="{2392E2C0-3805-405C-8D2F-BF2C933633BC}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
   <si>
     <t>Order_ID</t>
   </si>
@@ -76,13 +76,25 @@
   </si>
   <si>
     <t>Total Cost</t>
+  </si>
+  <si>
+    <t>SUM</t>
+  </si>
+  <si>
+    <t>COUNT</t>
+  </si>
+  <si>
+    <t>AVERAGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IF </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,16 +110,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -130,11 +155,53 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -142,12 +209,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -463,14 +546,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2656EAA7-A2F4-49D6-94FC-0BDC51781C8A}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -486,11 +569,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>101</v>
       </c>
@@ -506,12 +589,12 @@
       <c r="E2" s="2">
         <v>1</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="3">
         <f>D2*E2</f>
         <v>55000</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>103</v>
       </c>
@@ -527,12 +610,12 @@
       <c r="E3" s="2">
         <v>1</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <f>D3*E3</f>
         <v>18000</v>
       </c>
     </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>105</v>
       </c>
@@ -548,12 +631,12 @@
       <c r="E4" s="2">
         <v>1</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <f>D4*E4</f>
         <v>4000</v>
       </c>
     </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>102</v>
       </c>
@@ -569,12 +652,12 @@
       <c r="E5" s="2">
         <v>2</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <f>D5*E5</f>
         <v>6000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>104</v>
       </c>
@@ -590,12 +673,12 @@
       <c r="E6" s="2">
         <v>3</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <f>D6*E6</f>
         <v>7500</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -611,11 +694,23 @@
       <c r="E9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>101</v>
       </c>
@@ -631,12 +726,28 @@
       <c r="E10" s="2">
         <v>1</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="6">
         <f>D10*E10</f>
         <v>55000</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" s="12">
+        <f>SUM(F10:F14)</f>
+        <v>90500</v>
+      </c>
+      <c r="H10" s="12">
+        <f>AVERAGE(F10:F14)</f>
+        <v>18100</v>
+      </c>
+      <c r="I10" s="13">
+        <f>COUNT(F10:F14)</f>
+        <v>5</v>
+      </c>
+      <c r="J10" s="14" t="str">
+        <f>IF(F10&gt;10000, "High Sell", "Low Sell")</f>
+        <v>High Sell</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>103</v>
       </c>
@@ -652,12 +763,19 @@
       <c r="E11" s="2">
         <v>1</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="6">
         <f>D11*E11</f>
         <v>18000</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" s="8"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="14" t="str">
+        <f t="shared" ref="J11:J14" si="0">IF(F11&gt;10000, "High Sell", "Low Sell")</f>
+        <v>High Sell</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>105</v>
       </c>
@@ -673,12 +791,19 @@
       <c r="E12" s="2">
         <v>1</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="6">
         <f>D12*E12</f>
         <v>4000</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" s="8"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>Low Sell</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>102</v>
       </c>
@@ -694,12 +819,19 @@
       <c r="E13" s="2">
         <v>2</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="6">
         <f>D13*E13</f>
         <v>6000</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" s="8"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>Low Sell</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>104</v>
       </c>
@@ -715,9 +847,16 @@
       <c r="E14" s="2">
         <v>3</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="6">
         <f>D14*E14</f>
         <v>7500</v>
+      </c>
+      <c r="G14" s="9"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>Low Sell</v>
       </c>
     </row>
   </sheetData>
